--- a/Result/profitability/1608.xlsx
+++ b/Result/profitability/1608.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.74875</v>
+        <v>1.5575</v>
       </c>
       <c r="N2" t="n">
-        <v>9.223750000000001</v>
+        <v>9.546250000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7575</v>
+        <v>1.5725</v>
       </c>
       <c r="N3" t="n">
-        <v>8.827500000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7112499999999999</v>
+        <v>1.49875</v>
       </c>
       <c r="N4" t="n">
-        <v>8.063750000000001</v>
+        <v>7.70625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.97</v>
       </c>
       <c r="M5" t="n">
-        <v>0.41875</v>
+        <v>1.17125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9074999999999998</v>
+        <v>1.23125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3524999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.02625</v>
+        <v>-0.7512499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04875000000000006</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5124999999999997</v>
+        <v>-0.23125</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,25 +1391,25 @@
         <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06625000000000004</v>
+        <v>0.7212499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.09874999999999989</v>
+        <v>-0.4224999999999997</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>0.51</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04875000000000006</v>
+        <v>-0.04874999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6449999999999998</v>
+        <v>-0.6449999999999996</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.21</v>
       </c>
       <c r="M10" t="n">
-        <v>0.007499999999999941</v>
+        <v>0.00750000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01500000000000024</v>
+        <v>0.01500000000000046</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>-0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03625000000000006</v>
+        <v>-0.03624999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07125000000000026</v>
+        <v>0.07125000000000048</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>0.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03499999999999993</v>
+        <v>0.035</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3712500000000003</v>
+        <v>0.3712500000000005</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
         <v>0.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2824999999999999</v>
+        <v>0.2825</v>
       </c>
       <c r="N13" t="n">
-        <v>6.27375</v>
+        <v>6.273750000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3264</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2891</v>
+      </c>
+      <c r="E75" t="n">
+        <v>373</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>281</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2681</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2961</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2830</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.51625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>17.02702702702703</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1848679514632405</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.261538461538461</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2933182332955833</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
